--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589810</v>
+        <v>136833985</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>87374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630369</v>
+        <v>630315</v>
       </c>
       <c r="R2" t="n">
-        <v>6724601</v>
+        <v>6724621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,68 +770,76 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellinor Delin, Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589810</t>
+          <t>https://artportalen.se/Sighting/136833985</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129589931</v>
+        <v>136837901</v>
       </c>
       <c r="B3" t="n">
-        <v>96437</v>
+        <v>87581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630466</v>
+        <v>630516</v>
       </c>
       <c r="R3" t="n">
-        <v>6724600</v>
+        <v>6724582</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,71 +880,83 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589931</t>
+          <t>https://artportalen.se/Sighting/136837901</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131024934</v>
+        <v>136836671</v>
       </c>
       <c r="B4" t="n">
-        <v>96231</v>
+        <v>87416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630561</v>
+        <v>630358</v>
       </c>
       <c r="R4" t="n">
-        <v>6724696</v>
+        <v>6724437</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,17 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,65 +994,56 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>stort block</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024934</t>
+          <t>https://artportalen.se/Sighting/136836671</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589930</v>
+        <v>129589810</v>
       </c>
       <c r="B5" t="n">
-        <v>96338</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630407</v>
+        <v>630369</v>
       </c>
       <c r="R5" t="n">
-        <v>6724605</v>
+        <v>6724601</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,12 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1108,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Ellinor Delin, Jenny Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589930</t>
+          <t>https://artportalen.se/Sighting/129589810</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131024917</v>
+        <v>129589931</v>
       </c>
       <c r="B6" t="n">
-        <v>96458</v>
+        <v>96437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1131,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630350</v>
+        <v>630466</v>
       </c>
       <c r="R6" t="n">
-        <v>6724557</v>
+        <v>6724600</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,17 +1185,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,63 +1201,53 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>lövträdslåga</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024917</t>
+          <t>https://artportalen.se/Sighting/129589931</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131024929</v>
+        <v>131024934</v>
       </c>
       <c r="B7" t="n">
-        <v>91435</v>
+        <v>96231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5747</v>
+        <v>2779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630325</v>
+        <v>630561</v>
       </c>
       <c r="R7" t="n">
-        <v>6724586</v>
+        <v>6724696</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1295,7 +1297,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ljus fot, blekgula grenar, citrongula toppar, ca 1 dm hög, ingen lukt och smak i fält, men efter torkning påtaglig men svag lukt som drar mot anis, spormått stämmer. Stora Enso naturvärdesbedömning.</t>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,6 +1312,11 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>stort block</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1320,22 +1327,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024929</t>
+          <t>https://artportalen.se/Sighting/131024934</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129589927</v>
+        <v>129589930</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>96338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,38 +1350,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630322</v>
+        <v>630407</v>
       </c>
       <c r="R8" t="n">
-        <v>6724566</v>
+        <v>6724605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,11 +1412,6 @@
           <t>2025-07-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>gnag</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1437,16 +1435,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589927</t>
+          <t>https://artportalen.se/Sighting/129589930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129589942</v>
+        <v>131024917</v>
       </c>
       <c r="B9" t="n">
-        <v>8455</v>
+        <v>96458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,41 +1452,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630515</v>
+        <v>630350</v>
       </c>
       <c r="R9" t="n">
-        <v>6724590</v>
+        <v>6724557</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,17 +1506,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>gnag</t>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,66 +1527,87 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>lövträdslåga</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson, Ellinor Delin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589942</t>
+          <t>https://artportalen.se/Sighting/131024917</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589934</v>
+        <v>136833632</v>
       </c>
       <c r="B10" t="n">
-        <v>99096</v>
+        <v>87553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>3739</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630377</v>
+        <v>630315</v>
       </c>
       <c r="R10" t="n">
-        <v>6724468</v>
+        <v>6724591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,12 +1634,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,68 +1648,69 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589934</t>
+          <t>https://artportalen.se/Sighting/136833632</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129589991</v>
+        <v>136834313</v>
       </c>
       <c r="B11" t="n">
-        <v>99096</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>3739</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630424</v>
+        <v>630401</v>
       </c>
       <c r="R11" t="n">
-        <v>6724693</v>
+        <v>6724538</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,12 +1737,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,62 +1757,73 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589991</t>
+          <t>https://artportalen.se/Sighting/136834313</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129589997</v>
+        <v>136837881</v>
       </c>
       <c r="B12" t="n">
-        <v>99096</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>3739</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630493</v>
+        <v>630516</v>
       </c>
       <c r="R12" t="n">
-        <v>6724708</v>
+        <v>6724582</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,12 +1850,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,33 +1864,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589997</t>
+          <t>https://artportalen.se/Sighting/136837881</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131024932</v>
+        <v>136833324</v>
       </c>
       <c r="B13" t="n">
-        <v>99096</v>
+        <v>93407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,37 +1899,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>4363</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630419</v>
+        <v>630343</v>
       </c>
       <c r="R13" t="n">
-        <v>6724706</v>
+        <v>6724434</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1925,17 +1964,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,76 +1978,72 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024932</t>
+          <t>https://artportalen.se/Sighting/136833324</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129589943</v>
+        <v>131024929</v>
       </c>
       <c r="B14" t="n">
-        <v>102240</v>
+        <v>91435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>5747</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630516</v>
+        <v>630325</v>
       </c>
       <c r="R14" t="n">
-        <v>6724588</v>
+        <v>6724586</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,12 +2067,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ljus fot, blekgula grenar, citrongula toppar, ca 1 dm hög, ingen lukt och smak i fält, men efter torkning påtaglig men svag lukt som drar mot anis, spormått stämmer. Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2053,66 +2088,71 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson, Ellinor Delin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589943</t>
+          <t>https://artportalen.se/Sighting/131024929</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129589989</v>
+        <v>136833908</v>
       </c>
       <c r="B15" t="n">
-        <v>104627</v>
+        <v>91620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630408</v>
+        <v>630335</v>
       </c>
       <c r="R15" t="n">
-        <v>6724687</v>
+        <v>6724589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,12 +2179,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,62 +2199,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589989</t>
+          <t>https://artportalen.se/Sighting/136833908</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129589994</v>
+        <v>136834279</v>
       </c>
       <c r="B16" t="n">
-        <v>104627</v>
+        <v>93447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630512</v>
+        <v>630423</v>
       </c>
       <c r="R16" t="n">
-        <v>6724685</v>
+        <v>6724583</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,12 +2281,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,27 +2301,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589994</t>
+          <t>https://artportalen.se/Sighting/136834279</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589929</v>
+        <v>129589927</v>
       </c>
       <c r="B17" t="n">
-        <v>101325</v>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,34 +2329,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630391</v>
+        <v>630322</v>
       </c>
       <c r="R17" t="n">
-        <v>6724605</v>
+        <v>6724566</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2395,11 @@
           <t>2025-07-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>gnag</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2374,16 +2423,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589929</t>
+          <t>https://artportalen.se/Sighting/129589927</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129589932</v>
+        <v>129589942</v>
       </c>
       <c r="B18" t="n">
-        <v>101325</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,34 +2440,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630348</v>
+        <v>630515</v>
       </c>
       <c r="R18" t="n">
-        <v>6724453</v>
+        <v>6724590</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,12 +2498,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2476,16 +2534,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589932</t>
+          <t>https://artportalen.se/Sighting/129589942</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129589992</v>
+        <v>129589934</v>
       </c>
       <c r="B19" t="n">
-        <v>101325</v>
+        <v>99096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2493,21 +2551,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2575,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630439</v>
+        <v>630377</v>
       </c>
       <c r="R19" t="n">
-        <v>6724710</v>
+        <v>6724468</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,12 +2605,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2578,38 +2636,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589992</t>
+          <t>https://artportalen.se/Sighting/129589934</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129589809</v>
+        <v>129589991</v>
       </c>
       <c r="B20" t="n">
-        <v>93225</v>
+        <v>99096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6332770</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,10 +2677,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630397</v>
+        <v>630424</v>
       </c>
       <c r="R20" t="n">
-        <v>6724623</v>
+        <v>6724693</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2649,12 +2707,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,11 +2732,1163 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ellinor Delin, Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589991</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129589997</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>630493</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6724708</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589997</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131024932</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>630419</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6724706</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024932</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129589943</v>
+      </c>
+      <c r="B23" t="n">
+        <v>102240</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>630516</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6724588</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589943</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129589989</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>630408</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6724687</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589989</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129589994</v>
+      </c>
+      <c r="B25" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>630512</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6724685</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589994</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129589929</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>630391</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6724605</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589929</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129589932</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>630348</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6724453</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589932</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129589992</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>630439</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6724710</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589992</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136837380</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93425</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>630367</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6724487</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136837380</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136837383</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93438</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6331651</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Silkestaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellodon melilotinus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Quél.) Svantesson</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>630367</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6724487</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136837383</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129589809</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>630397</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6724623</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ellinor Delin, Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129589809</t>
         </is>
@@ -2705,6 +3915,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,27 +680,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136833985</v>
+        <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87374</v>
+        <v>87373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630315</v>
+        <v>630298</v>
       </c>
       <c r="R2" t="n">
-        <v>6724621</v>
+        <v>6724455</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,16 +798,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136833985</t>
+          <t>https://artportalen.se/Sighting/137001186</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136837901</v>
+        <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87581</v>
+        <v>87373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,22 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cortinarius aureofulvus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630516</v>
+        <v>630306</v>
       </c>
       <c r="R3" t="n">
-        <v>6724582</v>
+        <v>6724471</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,43 +922,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837901</t>
+          <t>https://artportalen.se/Sighting/137001187</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136836671</v>
+        <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87416</v>
+        <v>87374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -950,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630358</v>
+        <v>630315</v>
       </c>
       <c r="R4" t="n">
-        <v>6724437</v>
+        <v>6724621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,51 +1036,58 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136836671</t>
+          <t>https://artportalen.se/Sighting/136833985</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129589810</v>
+        <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>87581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>433</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630369</v>
+        <v>630516</v>
       </c>
       <c r="R5" t="n">
-        <v>6724601</v>
+        <v>6724582</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,12 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,71 +1128,68 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ellinor Delin, Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589810</t>
+          <t>https://artportalen.se/Sighting/136837901</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589931</v>
+        <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>96437</v>
+        <v>87581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>433</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630466</v>
+        <v>630442</v>
       </c>
       <c r="R6" t="n">
-        <v>6724600</v>
+        <v>6724703</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,12 +1213,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,65 +1243,76 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589931</t>
+          <t>https://artportalen.se/Sighting/137001197</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131024934</v>
+        <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>96231</v>
+        <v>87416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630561</v>
+        <v>630358</v>
       </c>
       <c r="R7" t="n">
-        <v>6724696</v>
+        <v>6724437</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,17 +1336,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,81 +1350,72 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>stort block</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024934</t>
+          <t>https://artportalen.se/Sighting/136836671</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129589930</v>
+        <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>96338</v>
+        <v>87416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630407</v>
+        <v>630398</v>
       </c>
       <c r="R8" t="n">
-        <v>6724605</v>
+        <v>6724545</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,12 +1439,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,65 +1469,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589930</t>
+          <t>https://artportalen.se/Sighting/137001192</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131024917</v>
+        <v>129589810</v>
       </c>
       <c r="B9" t="n">
-        <v>96458</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630350</v>
+        <v>630369</v>
       </c>
       <c r="R9" t="n">
-        <v>6724557</v>
+        <v>6724601</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,11 +1559,6 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1527,87 +1567,66 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>lövträdslåga</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Ellinor Delin, Jenny Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024917</t>
+          <t>https://artportalen.se/Sighting/129589810</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136833632</v>
+        <v>129589931</v>
       </c>
       <c r="B10" t="n">
-        <v>87553</v>
+        <v>96437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3739</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630315</v>
+        <v>630466</v>
       </c>
       <c r="R10" t="n">
-        <v>6724591</v>
+        <v>6724600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,12 +1653,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,56 +1667,55 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136833632</t>
+          <t>https://artportalen.se/Sighting/129589931</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136834313</v>
+        <v>131024934</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>96231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3739</v>
+        <v>2779</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1707,13 +1725,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630401</v>
+        <v>630561</v>
       </c>
       <c r="R11" t="n">
-        <v>6724538</v>
+        <v>6724696</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,12 +1755,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,77 +1776,76 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>stort block</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136834313</t>
+          <t>https://artportalen.se/Sighting/131024934</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136837881</v>
+        <v>129589930</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>96338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3739</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630516</v>
+        <v>630407</v>
       </c>
       <c r="R12" t="n">
-        <v>6724582</v>
+        <v>6724605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,12 +1872,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,34 +1886,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837881</t>
+          <t>https://artportalen.se/Sighting/129589930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136833324</v>
+        <v>131024917</v>
       </c>
       <c r="B13" t="n">
-        <v>93407</v>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,48 +1920,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4363</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630343</v>
+        <v>630350</v>
       </c>
       <c r="R13" t="n">
-        <v>6724434</v>
+        <v>6724557</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,12 +1974,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,72 +1993,92 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>lövträdslåga</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson, Ellinor Delin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136833324</t>
+          <t>https://artportalen.se/Sighting/131024917</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131024929</v>
+        <v>136833632</v>
       </c>
       <c r="B14" t="n">
-        <v>91435</v>
+        <v>87553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5747</v>
+        <v>3739</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630325</v>
+        <v>630315</v>
       </c>
       <c r="R14" t="n">
-        <v>6724586</v>
+        <v>6724591</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,17 +2102,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ljus fot, blekgula grenar, citrongula toppar, ca 1 dm hög, ingen lukt och smak i fält, men efter torkning påtaglig men svag lukt som drar mot anis, spormått stämmer. Stora Enso naturvärdesbedömning.</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,60 +2116,56 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024929</t>
+          <t>https://artportalen.se/Sighting/136833632</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136833908</v>
+        <v>136834313</v>
       </c>
       <c r="B15" t="n">
-        <v>91620</v>
+        <v>87553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5747</v>
+        <v>3739</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630335</v>
+        <v>630401</v>
       </c>
       <c r="R15" t="n">
-        <v>6724589</v>
+        <v>6724538</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,16 +2236,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136833908</t>
+          <t>https://artportalen.se/Sighting/136834313</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136834279</v>
+        <v>136837881</v>
       </c>
       <c r="B16" t="n">
-        <v>93447</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,34 +2253,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630423</v>
+        <v>630516</v>
       </c>
       <c r="R16" t="n">
-        <v>6724583</v>
+        <v>6724582</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,6 +2332,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2312,58 +2350,65 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136834279</t>
+          <t>https://artportalen.se/Sighting/136837881</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129589927</v>
+        <v>137001188</v>
       </c>
       <c r="B17" t="n">
-        <v>8455</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>3739</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630322</v>
+        <v>630357</v>
       </c>
       <c r="R17" t="n">
-        <v>6724566</v>
+        <v>6724529</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2387,17 +2432,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>gnag</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,33 +2456,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589927</t>
+          <t>https://artportalen.se/Sighting/137001188</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129589942</v>
+        <v>137001191</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>87324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,41 +2491,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>3762</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630515</v>
+        <v>630393</v>
       </c>
       <c r="R18" t="n">
-        <v>6724590</v>
+        <v>6724532</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,17 +2545,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>gnag</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2523,65 +2575,76 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589942</t>
+          <t>https://artportalen.se/Sighting/137001191</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129589934</v>
+        <v>137001181</v>
       </c>
       <c r="B19" t="n">
-        <v>99096</v>
+        <v>93403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630377</v>
+        <v>630375</v>
       </c>
       <c r="R19" t="n">
-        <v>6724468</v>
+        <v>6724441</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2605,12 +2668,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,33 +2692,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589934</t>
+          <t>https://artportalen.se/Sighting/137001181</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129589991</v>
+        <v>136833324</v>
       </c>
       <c r="B20" t="n">
-        <v>99096</v>
+        <v>93407</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2653,34 +2727,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>4363</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630424</v>
+        <v>630343</v>
       </c>
       <c r="R20" t="n">
-        <v>6724693</v>
+        <v>6724434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,12 +2792,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,71 +2806,72 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589991</t>
+          <t>https://artportalen.se/Sighting/136833324</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129589997</v>
+        <v>137001193</v>
       </c>
       <c r="B21" t="n">
-        <v>99096</v>
+        <v>93423</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630493</v>
+        <v>630376</v>
       </c>
       <c r="R21" t="n">
-        <v>6724708</v>
+        <v>6724518</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2809,12 +2895,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,49 +2925,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589997</t>
+          <t>https://artportalen.se/Sighting/137001193</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131024932</v>
+        <v>131024929</v>
       </c>
       <c r="B22" t="n">
-        <v>99096</v>
+        <v>91435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2881,10 +2977,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630419</v>
+        <v>630325</v>
       </c>
       <c r="R22" t="n">
-        <v>6724706</v>
+        <v>6724586</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2921,7 +3017,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>Ljus fot, blekgula grenar, citrongula toppar, ca 1 dm hög, ingen lukt och smak i fält, men efter torkning påtaglig men svag lukt som drar mot anis, spormått stämmer. Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,57 +3042,57 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jenny Andersson, Ellinor Delin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024932</t>
+          <t>https://artportalen.se/Sighting/131024929</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129589943</v>
+        <v>136833908</v>
       </c>
       <c r="B23" t="n">
-        <v>102240</v>
+        <v>91620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221235</v>
+        <v>5747</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630516</v>
+        <v>630335</v>
       </c>
       <c r="R23" t="n">
-        <v>6724588</v>
+        <v>6724589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,12 +3119,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,65 +3139,76 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589943</t>
+          <t>https://artportalen.se/Sighting/136833908</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129589989</v>
+        <v>137001184</v>
       </c>
       <c r="B24" t="n">
-        <v>104627</v>
+        <v>91620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630408</v>
+        <v>630368</v>
       </c>
       <c r="R24" t="n">
-        <v>6724687</v>
+        <v>6724430</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3125,12 +3232,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,68 +3256,69 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589989</t>
+          <t>https://artportalen.se/Sighting/137001184</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129589994</v>
+        <v>136834279</v>
       </c>
       <c r="B25" t="n">
-        <v>104627</v>
+        <v>93447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630512</v>
+        <v>630423</v>
       </c>
       <c r="R25" t="n">
-        <v>6724685</v>
+        <v>6724583</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,12 +3345,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,27 +3365,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589994</t>
+          <t>https://artportalen.se/Sighting/136834279</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129589929</v>
+        <v>129589927</v>
       </c>
       <c r="B26" t="n">
-        <v>101325</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,34 +3393,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630391</v>
+        <v>630322</v>
       </c>
       <c r="R26" t="n">
-        <v>6724605</v>
+        <v>6724566</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,6 +3459,11 @@
           <t>2025-07-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>gnag</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3360,16 +3487,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589929</t>
+          <t>https://artportalen.se/Sighting/129589927</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129589932</v>
+        <v>129589942</v>
       </c>
       <c r="B27" t="n">
-        <v>101325</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,34 +3504,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630348</v>
+        <v>630515</v>
       </c>
       <c r="R27" t="n">
-        <v>6724453</v>
+        <v>6724590</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,12 +3562,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,16 +3598,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589932</t>
+          <t>https://artportalen.se/Sighting/129589942</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129589992</v>
+        <v>129589934</v>
       </c>
       <c r="B28" t="n">
-        <v>101325</v>
+        <v>99096</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3615,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3639,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630439</v>
+        <v>630377</v>
       </c>
       <c r="R28" t="n">
-        <v>6724710</v>
+        <v>6724468</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,12 +3669,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,58 +3700,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589992</t>
+          <t>https://artportalen.se/Sighting/129589934</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136837380</v>
+        <v>129589991</v>
       </c>
       <c r="B29" t="n">
-        <v>93425</v>
+        <v>99096</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6047725</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630367</v>
+        <v>630424</v>
       </c>
       <c r="R29" t="n">
-        <v>6724487</v>
+        <v>6724693</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,12 +3771,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,80 +3785,68 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837380</t>
+          <t>https://artportalen.se/Sighting/129589991</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136837383</v>
+        <v>129589997</v>
       </c>
       <c r="B30" t="n">
-        <v>93438</v>
+        <v>99096</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6331651</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Silkestaggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon melilotinus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Quél.) Svantesson</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630367</v>
+        <v>630493</v>
       </c>
       <c r="R30" t="n">
-        <v>6724487</v>
+        <v>6724708</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3756,12 +3873,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,72 +3887,71 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837383</t>
+          <t>https://artportalen.se/Sighting/129589997</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129589809</v>
+        <v>131024932</v>
       </c>
       <c r="B31" t="n">
-        <v>93225</v>
+        <v>99096</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6332770</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630397</v>
+        <v>630419</v>
       </c>
       <c r="R31" t="n">
-        <v>6724623</v>
+        <v>6724706</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3867,6 +3983,11 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3875,20 +3996,1321 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ellinor Delin, Jenny Andersson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024932</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129589943</v>
+      </c>
+      <c r="B32" t="n">
+        <v>102240</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>630516</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6724588</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589943</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129589989</v>
+      </c>
+      <c r="B33" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>630408</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6724687</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589989</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129589994</v>
+      </c>
+      <c r="B34" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>630512</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6724685</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589994</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129589929</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>630391</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6724605</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589929</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129589932</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>630348</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6724453</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589932</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129589992</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>630439</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6724710</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589992</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137001180</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93426</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6010747</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosellum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Nitare</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>630358</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6724424</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fruktkroppar små mellan 3 - 9 cm breda något fjälliga brun till ljusbruna hattar och avsmalnande blågrå fotbas. Liten häxring i äldre barrblandskog med tydlig kalkpåverkan tillsammans med friskmossor och blåsippa.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137001180</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136837380</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93425</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>630367</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6724487</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136837380</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136837383</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93438</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6331651</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Silkestaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellodon melilotinus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Quél.) Svantesson</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>630367</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6724487</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136837383</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137001183</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93438</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6331651</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Silkestaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellodon melilotinus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Quél.) Svantesson</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>630364</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6724431</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137001183</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137001196</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93438</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6331651</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Silkestaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellodon melilotinus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Quél.) Svantesson</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>630414</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6724648</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137001196</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129589809</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>630397</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6724623</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ellinor Delin, Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129589809</t>
         </is>
@@ -3926,6 +5348,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87373</v>
+        <v>87375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87373</v>
+        <v>87375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87374</v>
+        <v>87376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87581</v>
+        <v>87583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87581</v>
+        <v>87583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87416</v>
+        <v>87418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87416</v>
+        <v>87418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,48 +1486,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129589810</v>
+        <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>87418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Torvstig, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630369</v>
+        <v>630338</v>
       </c>
       <c r="R9" t="n">
-        <v>6724601</v>
+        <v>6724403</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,12 +1554,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,49 +1584,53 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ellinor Delin, Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589810</t>
+          <t>https://artportalen.se/Sighting/137024404</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129589931</v>
+        <v>129589810</v>
       </c>
       <c r="B10" t="n">
-        <v>96437</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630466</v>
+        <v>630369</v>
       </c>
       <c r="R10" t="n">
-        <v>6724600</v>
+        <v>6724601</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,12 +1670,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,22 +1695,22 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Ellinor Delin, Jenny Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589931</t>
+          <t>https://artportalen.se/Sighting/129589810</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131024934</v>
+        <v>129589931</v>
       </c>
       <c r="B11" t="n">
-        <v>96231</v>
+        <v>96437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,37 +1718,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630561</v>
+        <v>630466</v>
       </c>
       <c r="R11" t="n">
-        <v>6724696</v>
+        <v>6724600</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,17 +1772,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,41 +1788,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>stort block</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024934</t>
+          <t>https://artportalen.se/Sighting/129589931</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129589930</v>
+        <v>131024934</v>
       </c>
       <c r="B12" t="n">
-        <v>96338</v>
+        <v>96231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,37 +1820,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>2779</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630407</v>
+        <v>630561</v>
       </c>
       <c r="R12" t="n">
-        <v>6724605</v>
+        <v>6724696</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,12 +1874,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1888,31 +1895,41 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>stort block</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589930</t>
+          <t>https://artportalen.se/Sighting/131024934</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131024917</v>
+        <v>129589930</v>
       </c>
       <c r="B13" t="n">
-        <v>96458</v>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,37 +1937,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630350</v>
+        <v>630407</v>
       </c>
       <c r="R13" t="n">
-        <v>6724557</v>
+        <v>6724605</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,17 +1991,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,90 +2007,69 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>lövträdslåga</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024917</t>
+          <t>https://artportalen.se/Sighting/129589930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136833632</v>
+        <v>131024917</v>
       </c>
       <c r="B14" t="n">
-        <v>87553</v>
+        <v>96458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3739</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630315</v>
+        <v>630350</v>
       </c>
       <c r="R14" t="n">
-        <v>6724591</v>
+        <v>6724557</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2102,12 +2093,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,34 +2112,43 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>lövträdslåga</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson, Ellinor Delin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136833632</t>
+          <t>https://artportalen.se/Sighting/131024917</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136834313</v>
+        <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,17 +2173,28 @@
           <t>Quél.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630401</v>
+        <v>630315</v>
       </c>
       <c r="R15" t="n">
-        <v>6724538</v>
+        <v>6724591</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,6 +2235,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2236,16 +2253,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136834313</t>
+          <t>https://artportalen.se/Sighting/136833632</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136837881</v>
+        <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,28 +2287,17 @@
           <t>Quél.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630516</v>
+        <v>630401</v>
       </c>
       <c r="R16" t="n">
-        <v>6724582</v>
+        <v>6724538</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2338,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2350,16 +2355,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837881</t>
+          <t>https://artportalen.se/Sighting/136834313</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137001188</v>
+        <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,13 +2407,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630357</v>
+        <v>630516</v>
       </c>
       <c r="R17" t="n">
-        <v>6724529</v>
+        <v>6724582</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2432,22 +2437,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,51 +2469,62 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137001188</t>
+          <t>https://artportalen.se/Sighting/136837881</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137001191</v>
+        <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87324</v>
+        <v>87555</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3762</v>
+        <v>3739</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630393</v>
+        <v>630357</v>
       </c>
       <c r="R18" t="n">
-        <v>6724532</v>
+        <v>6724529</v>
       </c>
       <c r="S18" t="n">
         <v>6</v>
@@ -2550,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2560,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,6 +2575,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2586,65 +2593,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137001191</t>
+          <t>https://artportalen.se/Sighting/137001188</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137001181</v>
+        <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>93403</v>
+        <v>87326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630375</v>
+        <v>630393</v>
       </c>
       <c r="R19" t="n">
-        <v>6724441</v>
+        <v>6724532</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,7 +2688,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2710,43 +2705,43 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137001181</t>
+          <t>https://artportalen.se/Sighting/137001191</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136833324</v>
+        <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93407</v>
+        <v>93405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2762,13 +2757,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630343</v>
+        <v>630375</v>
       </c>
       <c r="R20" t="n">
-        <v>6724434</v>
+        <v>6724441</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2792,12 +2787,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,54 +2829,65 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136833324</t>
+          <t>https://artportalen.se/Sighting/137001181</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137001193</v>
+        <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93423</v>
+        <v>93409</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>4363</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630376</v>
+        <v>630343</v>
       </c>
       <c r="R21" t="n">
-        <v>6724518</v>
+        <v>6724434</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2895,22 +2911,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,6 +2925,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2936,38 +2943,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137001193</t>
+          <t>https://artportalen.se/Sighting/136833324</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131024929</v>
+        <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>91435</v>
+        <v>93425</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,13 +2984,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630325</v>
+        <v>630376</v>
       </c>
       <c r="R22" t="n">
-        <v>6724586</v>
+        <v>6724518</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3007,17 +3014,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ljus fot, blekgula grenar, citrongula toppar, ca 1 dm hög, ingen lukt och smak i fält, men efter torkning påtaglig men svag lukt som drar mot anis, spormått stämmer. Stora Enso naturvärdesbedömning.</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3028,36 +3040,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024929</t>
+          <t>https://artportalen.se/Sighting/137001193</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136833908</v>
+        <v>131024929</v>
       </c>
       <c r="B23" t="n">
-        <v>91620</v>
+        <v>91435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,13 +3096,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630335</v>
+        <v>630325</v>
       </c>
       <c r="R23" t="n">
-        <v>6724589</v>
+        <v>6724586</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3119,12 +3126,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ljus fot, blekgula grenar, citrongula toppar, ca 1 dm hög, ingen lukt och smak i fält, men efter torkning påtaglig men svag lukt som drar mot anis, spormått stämmer. Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3135,31 +3147,36 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson, Ellinor Delin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136833908</t>
+          <t>https://artportalen.se/Sighting/131024929</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137001184</v>
+        <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,31 +3201,20 @@
           <t>Christan</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630368</v>
+        <v>630335</v>
       </c>
       <c r="R24" t="n">
-        <v>6724430</v>
+        <v>6724589</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,22 +3238,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,7 +3252,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3274,54 +3269,65 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137001184</t>
+          <t>https://artportalen.se/Sighting/136833908</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136834279</v>
+        <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>93447</v>
+        <v>91622</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630423</v>
+        <v>630368</v>
       </c>
       <c r="R25" t="n">
-        <v>6724583</v>
+        <v>6724430</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3345,12 +3351,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3359,6 +3375,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3376,55 +3393,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136834279</t>
+          <t>https://artportalen.se/Sighting/137001184</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129589927</v>
+        <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>8455</v>
+        <v>93449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630322</v>
+        <v>630423</v>
       </c>
       <c r="R26" t="n">
-        <v>6724566</v>
+        <v>6724583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,17 +3464,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>gnag</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,69 +3484,68 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589927</t>
+          <t>https://artportalen.se/Sighting/136834279</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129589942</v>
+        <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>8455</v>
+        <v>93449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Torvstig, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630515</v>
+        <v>630338</v>
       </c>
       <c r="R27" t="n">
-        <v>6724590</v>
+        <v>6724403</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3562,17 +3569,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>gnag</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,27 +3599,31 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589942</t>
+          <t>https://artportalen.se/Sighting/137024420</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129589934</v>
+        <v>129589927</v>
       </c>
       <c r="B28" t="n">
-        <v>99096</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,34 +3631,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630377</v>
+        <v>630322</v>
       </c>
       <c r="R28" t="n">
-        <v>6724468</v>
+        <v>6724566</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3677,6 +3697,11 @@
           <t>2025-07-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>gnag</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3700,16 +3725,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589934</t>
+          <t>https://artportalen.se/Sighting/129589927</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129589991</v>
+        <v>129589942</v>
       </c>
       <c r="B29" t="n">
-        <v>99096</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,34 +3742,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630424</v>
+        <v>630515</v>
       </c>
       <c r="R29" t="n">
-        <v>6724693</v>
+        <v>6724590</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3771,12 +3800,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3802,13 +3836,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589991</t>
+          <t>https://artportalen.se/Sighting/129589942</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129589997</v>
+        <v>129589934</v>
       </c>
       <c r="B30" t="n">
         <v>99096</v>
@@ -3843,10 +3877,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630493</v>
+        <v>630377</v>
       </c>
       <c r="R30" t="n">
-        <v>6724708</v>
+        <v>6724468</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3873,12 +3907,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3904,13 +3938,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589997</t>
+          <t>https://artportalen.se/Sighting/129589934</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131024932</v>
+        <v>129589991</v>
       </c>
       <c r="B31" t="n">
         <v>99096</v>
@@ -3941,17 +3975,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630419</v>
+        <v>630424</v>
       </c>
       <c r="R31" t="n">
-        <v>6724706</v>
+        <v>6724693</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3975,17 +4009,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3996,58 +4025,53 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131024932</t>
+          <t>https://artportalen.se/Sighting/129589991</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129589943</v>
+        <v>129589997</v>
       </c>
       <c r="B32" t="n">
-        <v>102240</v>
+        <v>99096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4057,10 +4081,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630516</v>
+        <v>630493</v>
       </c>
       <c r="R32" t="n">
-        <v>6724588</v>
+        <v>6724708</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4087,12 +4111,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4118,16 +4142,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589943</t>
+          <t>https://artportalen.se/Sighting/129589997</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129589989</v>
+        <v>131024932</v>
       </c>
       <c r="B33" t="n">
-        <v>104627</v>
+        <v>99096</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,37 +4159,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630408</v>
+        <v>630419</v>
       </c>
       <c r="R33" t="n">
-        <v>6724687</v>
+        <v>6724706</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4189,12 +4213,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4205,53 +4234,58 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589989</t>
+          <t>https://artportalen.se/Sighting/131024932</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129589994</v>
+        <v>129589943</v>
       </c>
       <c r="B34" t="n">
-        <v>104627</v>
+        <v>102240</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4261,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630512</v>
+        <v>630516</v>
       </c>
       <c r="R34" t="n">
-        <v>6724685</v>
+        <v>6724588</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4291,12 +4325,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4322,16 +4356,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589994</t>
+          <t>https://artportalen.se/Sighting/129589943</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129589929</v>
+        <v>129589989</v>
       </c>
       <c r="B35" t="n">
-        <v>101325</v>
+        <v>104627</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4339,21 +4373,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4363,10 +4397,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630391</v>
+        <v>630408</v>
       </c>
       <c r="R35" t="n">
-        <v>6724605</v>
+        <v>6724687</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4393,12 +4427,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4424,16 +4458,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589929</t>
+          <t>https://artportalen.se/Sighting/129589989</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129589932</v>
+        <v>129589994</v>
       </c>
       <c r="B36" t="n">
-        <v>101325</v>
+        <v>104627</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4441,21 +4475,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4465,10 +4499,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630348</v>
+        <v>630512</v>
       </c>
       <c r="R36" t="n">
-        <v>6724453</v>
+        <v>6724685</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4495,12 +4529,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4526,13 +4560,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589932</t>
+          <t>https://artportalen.se/Sighting/129589994</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129589992</v>
+        <v>129589929</v>
       </c>
       <c r="B37" t="n">
         <v>101325</v>
@@ -4567,10 +4601,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630439</v>
+        <v>630391</v>
       </c>
       <c r="R37" t="n">
-        <v>6724710</v>
+        <v>6724605</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4597,12 +4631,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4628,65 +4662,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129589992</t>
+          <t>https://artportalen.se/Sighting/129589929</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137001180</v>
+        <v>129589932</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>101325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6010747</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgtaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nitare</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630358</v>
+        <v>630348</v>
       </c>
       <c r="R38" t="n">
-        <v>6724424</v>
+        <v>6724453</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4710,27 +4733,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Fruktkroppar små mellan 3 - 9 cm breda något fjälliga brun till ljusbruna hattar och avsmalnande blågrå fotbas. Liten häxring i äldre barrblandskog med tydlig kalkpåverkan tillsammans med friskmossor och blåsippa.</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4739,81 +4747,68 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137001180</t>
+          <t>https://artportalen.se/Sighting/129589932</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136837380</v>
+        <v>129589992</v>
       </c>
       <c r="B39" t="n">
-        <v>93425</v>
+        <v>101325</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6047725</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630367</v>
+        <v>630439</v>
       </c>
       <c r="R39" t="n">
-        <v>6724487</v>
+        <v>6724710</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4840,12 +4835,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4854,61 +4849,60 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837380</t>
+          <t>https://artportalen.se/Sighting/129589992</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136837383</v>
+        <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93438</v>
+        <v>93428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6331651</v>
+        <v>6010747</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Silkestaggsvamp</t>
+          <t>Dvärgtaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon melilotinus</t>
+          <t>Hydnellum scabrosellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Quél.) Svantesson</t>
+          <t>Nitare</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4924,13 +4918,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630367</v>
+        <v>630358</v>
       </c>
       <c r="R40" t="n">
-        <v>6724487</v>
+        <v>6724424</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4954,12 +4948,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fruktkroppar små mellan 3 - 9 cm breda något fjälliga brun till ljusbruna hattar och avsmalnande blågrå fotbas. Liten häxring i äldre barrblandskog med tydlig kalkpåverkan tillsammans med friskmossor och blåsippa.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4972,6 +4981,11 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
@@ -4986,54 +5000,61 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837383</t>
+          <t>https://artportalen.se/Sighting/137001180</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137001183</v>
+        <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93438</v>
+        <v>93427</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6331651</v>
+        <v>6047725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Silkestaggsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon melilotinus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Quél.) Svantesson</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>630364</v>
+        <v>630367</v>
       </c>
       <c r="R41" t="n">
-        <v>6724431</v>
+        <v>6724487</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5057,22 +5078,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,6 +5092,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5098,16 +5110,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137001183</t>
+          <t>https://artportalen.se/Sighting/136837380</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137001196</v>
+        <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5132,20 +5144,31 @@
           <t>(Quél.) Svantesson</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630414</v>
+        <v>630367</v>
       </c>
       <c r="R42" t="n">
-        <v>6724648</v>
+        <v>6724487</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5169,22 +5192,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,6 +5206,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5210,54 +5224,54 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137001196</t>
+          <t>https://artportalen.se/Sighting/136837383</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129589809</v>
+        <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93225</v>
+        <v>93440</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6332770</v>
+        <v>6331651</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Silkestaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon melilotinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Quél.) Svantesson</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630397</v>
+        <v>630364</v>
       </c>
       <c r="R43" t="n">
-        <v>6724623</v>
+        <v>6724431</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5281,12 +5295,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,16 +5325,230 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ellinor Delin, Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137001183</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137001196</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93440</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6331651</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Silkestaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellodon melilotinus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Quél.) Svantesson</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>630414</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6724648</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137001196</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129589809</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>630397</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6724623</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ellinor Delin, Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129589809</t>
         </is>
@@ -5360,6 +5598,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87375</v>
+        <v>87377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87375</v>
+        <v>87377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87376</v>
+        <v>87378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87418</v>
+        <v>87420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87418</v>
+        <v>87420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87418</v>
+        <v>87420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87326</v>
+        <v>87328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93428</v>
+        <v>93430</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87377</v>
+        <v>87378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87377</v>
+        <v>87378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87378</v>
+        <v>87379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87585</v>
+        <v>87586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87585</v>
+        <v>87586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87420</v>
+        <v>87421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87420</v>
+        <v>87421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87420</v>
+        <v>87421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93430</v>
+        <v>93431</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93442</v>
+        <v>93443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93442</v>
+        <v>93443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87378</v>
+        <v>87384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87378</v>
+        <v>87384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87379</v>
+        <v>87385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87586</v>
+        <v>87592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87586</v>
+        <v>87592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87421</v>
+        <v>87427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87421</v>
+        <v>87427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87421</v>
+        <v>87427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93412</v>
+        <v>93418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93431</v>
+        <v>93437</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93430</v>
+        <v>93436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93443</v>
+        <v>93449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93443</v>
+        <v>93449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93443</v>
+        <v>93449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87384</v>
+        <v>87388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87384</v>
+        <v>87388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87385</v>
+        <v>87389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87592</v>
+        <v>87596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87592</v>
+        <v>87596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87427</v>
+        <v>87431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87427</v>
+        <v>87431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87427</v>
+        <v>87431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93418</v>
+        <v>93422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93437</v>
+        <v>93441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93436</v>
+        <v>93440</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93449</v>
+        <v>93453</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93449</v>
+        <v>93453</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93449</v>
+        <v>93453</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87388</v>
+        <v>87390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87388</v>
+        <v>87390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87389</v>
+        <v>87391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87596</v>
+        <v>87598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87596</v>
+        <v>87598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87431</v>
+        <v>87433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87431</v>
+        <v>87433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87431</v>
+        <v>87433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93422</v>
+        <v>93424</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93441</v>
+        <v>93443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87390</v>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87390</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87391</v>
+        <v>87404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87598</v>
+        <v>87611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87598</v>
+        <v>87611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87433</v>
+        <v>87446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87433</v>
+        <v>87446</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87433</v>
+        <v>87446</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Amanda Sandberg</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Amanda Sandberg, Johan Lindell</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93424</v>
+        <v>93437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Johan Lindell</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93443</v>
+        <v>93456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93442</v>
+        <v>93455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93455</v>
+        <v>93468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93455</v>
+        <v>93468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93455</v>
+        <v>93468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87404</v>
+        <v>87406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87446</v>
+        <v>87448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87446</v>
+        <v>87448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87446</v>
+        <v>87448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93437</v>
+        <v>93438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93456</v>
+        <v>93457</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93468</v>
+        <v>93469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93468</v>
+        <v>93469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93468</v>
+        <v>93469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87405</v>
+        <v>87408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87405</v>
+        <v>87408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>87409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87448</v>
+        <v>87451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87448</v>
+        <v>87451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87448</v>
+        <v>87451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93457</v>
+        <v>93460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93456</v>
+        <v>93459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93469</v>
+        <v>93472</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93469</v>
+        <v>93472</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93469</v>
+        <v>93472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87408</v>
+        <v>87418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87408</v>
+        <v>87418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87409</v>
+        <v>87419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87451</v>
+        <v>87461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87451</v>
+        <v>87461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87451</v>
+        <v>87461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93441</v>
+        <v>93451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93460</v>
+        <v>93470</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93459</v>
+        <v>93469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93472</v>
+        <v>93482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93472</v>
+        <v>93482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93472</v>
+        <v>93482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87418</v>
+        <v>87419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87418</v>
+        <v>87419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87419</v>
+        <v>87420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91665</v>
+        <v>91666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91665</v>
+        <v>91666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93470</v>
+        <v>93471</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93482</v>
+        <v>93483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93482</v>
+        <v>93483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93482</v>
+        <v>93483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Amanda Sandberg, Johan Lindell</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Amanda Sandberg, Johan Lindell, Beke Regelin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Johan Lindell</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Johan Lindell, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87419</v>
+        <v>87422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87419</v>
+        <v>87422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87420</v>
+        <v>87423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87462</v>
+        <v>87465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87462</v>
+        <v>87465</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87462</v>
+        <v>87465</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Amanda Sandberg, Johan Lindell, Beke Regelin</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Amanda Sandberg, Johan Lindell</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93452</v>
+        <v>93457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91666</v>
+        <v>91669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91666</v>
+        <v>91669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Johan Lindell, Beke Regelin</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Johan Lindell</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93471</v>
+        <v>93476</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93470</v>
+        <v>93475</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93483</v>
+        <v>93488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93483</v>
+        <v>93488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93483</v>
+        <v>93488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91669</v>
+        <v>91671</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91669</v>
+        <v>91671</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93476</v>
+        <v>93478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93475</v>
+        <v>93477</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93488</v>
+        <v>93490</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93488</v>
+        <v>93490</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93488</v>
+        <v>93490</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87422</v>
+        <v>87427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87422</v>
+        <v>87427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87423</v>
+        <v>87428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93459</v>
+        <v>93465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91671</v>
+        <v>91676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91671</v>
+        <v>91676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93478</v>
+        <v>93484</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93477</v>
+        <v>93483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93490</v>
+        <v>93496</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93490</v>
+        <v>93496</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93490</v>
+        <v>93496</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87427</v>
+        <v>87438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87427</v>
+        <v>87438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87428</v>
+        <v>87439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93465</v>
+        <v>93477</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93484</v>
+        <v>93496</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93483</v>
+        <v>93495</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93496</v>
+        <v>93508</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93496</v>
+        <v>93508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93496</v>
+        <v>93508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87438</v>
+        <v>87439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87438</v>
+        <v>87439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87439</v>
+        <v>87440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93496</v>
+        <v>93497</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93495</v>
+        <v>93496</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93508</v>
+        <v>93509</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93508</v>
+        <v>93509</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93508</v>
+        <v>93509</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87439</v>
+        <v>87442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87439</v>
+        <v>87442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136833985</v>
       </c>
       <c r="B4" t="n">
-        <v>87440</v>
+        <v>87443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136837901</v>
       </c>
       <c r="B5" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136836671</v>
       </c>
       <c r="B7" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Amanda Sandberg, Johan Lindell</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Amanda Sandberg, Johan Lindell, Beke Regelin, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2148,7 +2148,7 @@
         <v>136833632</v>
       </c>
       <c r="B15" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>136834313</v>
       </c>
       <c r="B16" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136837881</v>
       </c>
       <c r="B17" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136833324</v>
       </c>
       <c r="B21" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>136833908</v>
       </c>
       <c r="B24" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>136834279</v>
       </c>
       <c r="B26" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Johan Lindell</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Johan Lindell, Beke Regelin, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93497</v>
+        <v>93500</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>136837380</v>
       </c>
       <c r="B41" t="n">
-        <v>93496</v>
+        <v>93499</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136837383</v>
       </c>
       <c r="B42" t="n">
-        <v>93509</v>
+        <v>93512</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93509</v>
+        <v>93512</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93509</v>
+        <v>93512</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Amanda Sandberg, Johan Lindell, Beke Regelin, Niklas Hjort</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Amanda Sandberg, Johan Lindell</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Johan Lindell, Beke Regelin, Niklas Hjort</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Eva Grönlund, kristina stenmarck, Majken Ekstrand, Mattias Andersson, Niklas Hjort, Beke Regelin, Johan Lindell</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87442</v>
+        <v>87443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87650</v>
+        <v>87651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87622</v>
+        <v>87623</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91692</v>
+        <v>91693</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137001186</v>
       </c>
       <c r="B2" t="n">
-        <v>87442</v>
+        <v>87446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137001187</v>
       </c>
       <c r="B3" t="n">
-        <v>87443</v>
+        <v>87446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137001197</v>
       </c>
       <c r="B6" t="n">
-        <v>87651</v>
+        <v>87654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137001192</v>
       </c>
       <c r="B8" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137024404</v>
       </c>
       <c r="B9" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>137001188</v>
       </c>
       <c r="B18" t="n">
-        <v>87623</v>
+        <v>87626</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137001191</v>
       </c>
       <c r="B19" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137001181</v>
       </c>
       <c r="B20" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137001193</v>
       </c>
       <c r="B22" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>137001184</v>
       </c>
       <c r="B25" t="n">
-        <v>91693</v>
+        <v>91696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>137024420</v>
       </c>
       <c r="B27" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>137001180</v>
       </c>
       <c r="B40" t="n">
-        <v>93500</v>
+        <v>93504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>137001183</v>
       </c>
       <c r="B43" t="n">
-        <v>93513</v>
+        <v>93516</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137001196</v>
       </c>
       <c r="B44" t="n">
-        <v>93513</v>
+        <v>93516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
